--- a/OfficeIMO.TestAssets/Documents/ExcelPivotCorpus/AllErrorRanking/top-count-two.xlsx
+++ b/OfficeIMO.TestAssets/Documents/ExcelPivotCorpus/AllErrorRanking/top-count-two.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\przemyslaw.klys.EVOTEC\.codex\worktrees\excel-csv-quality\OfficeIMO\OfficeIMO.TestAssets\Documents\ExcelPivotCorpus\AllErrorRanking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6FABB907-C0A4-463E-B980-C799590E2F2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C104C1B0-61C7-45AC-9790-6C4367ABF6FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="16170" windowWidth="28996" windowHeight="15675" xr2:uid="{23ABA173-2166-446D-BC18-823BE68E979A}"/>
+    <workbookView xWindow="-98" yWindow="16170" windowWidth="28996" windowHeight="15675" xr2:uid="{F177EC1D-DE6B-4F0C-9A25-DAD5E71050C6}"/>
   </bookViews>
   <sheets>
     <sheet name="Grouped" sheetId="2" r:id="rId1"/>
@@ -122,7 +122,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46293.576847337965" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="3" xr:uid="{D66896D3-E4A1-4395-B5FE-7E2A9312BFDD}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46293.579410763887" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="3" xr:uid="{6691ED51-247A-4B6F-92F8-EC13FCA6501F}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:B4" sheet="Source"/>
   </cacheSource>
@@ -164,7 +164,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{832790A9-EF93-4437-96F7-D033DC5C3C7C}" name="AllErrorPivot" cacheId="23" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CDFCC2E3-8DCD-4945-B0BC-851E33A7FB66}" name="AllErrorPivot" cacheId="23" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A4:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="2">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" measureFilter="1">
@@ -534,7 +534,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE7AB438-E7B7-427E-8A47-3C60464F46AD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EEF1E43-B9CE-41A8-98E1-418499C99B9A}">
   <dimension ref="A4:B7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -580,7 +580,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DAB5572-36AE-4453-8263-B570AF05F911}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DCBE68E-A116-4404-8DB7-5C2A9F2BD323}">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
